--- a/filer/38841297_silvan.xlsx
+++ b/filer/38841297_silvan.xlsx
@@ -615,7 +615,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (valuta pr. år - se kolonneoverskrifter)</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Resultatopgørelse t.kr.</t>
+          <t>Resultatopgørelse valuta pr. år - se kolonneoverskrifter</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -1494,7 +1494,7 @@
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>AKTIVER t.kr.</t>
+          <t>AKTIVER valuta pr. år - se kolonneoverskrifter</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
@@ -2972,7 +2972,7 @@
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>PASSIVER t.kr.</t>
+          <t>PASSIVER valuta pr. år - se kolonneoverskrifter</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
@@ -4765,7 +4765,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Resultatopgørelse &amp; nøgleoplysninger (t.kr.)</t>
+          <t>Resultatopgørelse &amp; nøgleoplysninger (valuta pr. år - se kolonneoverskrifter)</t>
         </is>
       </c>
       <c r="B1" s="3" t="n">
@@ -5188,7 +5188,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Balance (t.kr.)</t>
+          <t>Balance (valuta pr. år - se kolonneoverskrifter)</t>
         </is>
       </c>
       <c r="B1" s="3" t="n">
@@ -7280,15 +7280,15 @@
         </is>
       </c>
       <c r="B61" s="29">
-        <f>IF('balance_raw_38841297'!$F$31="","—",IF(ABS(B21-'balance_raw_38841297'!$F$31)&lt;=1,"✓ OK","❌ "&amp;TEXT(B21-'balance_raw_38841297'!$F$31,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_38841297'!$F$31="","—",IF(ABS(B21-'balance_raw_38841297'!$F$31)&lt;=1,"✓ OK","❌ "&amp;TEXT(B21-'balance_raw_38841297'!$F$31,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="C61" s="29">
-        <f>IF('balance_raw_38841297'!$E$31="","—",IF(ABS(C21-'balance_raw_38841297'!$E$31)&lt;=1,"✓ OK","❌ "&amp;TEXT(C21-'balance_raw_38841297'!$E$31,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_38841297'!$E$31="","—",IF(ABS(C21-'balance_raw_38841297'!$E$31)&lt;=1,"✓ OK","❌ "&amp;TEXT(C21-'balance_raw_38841297'!$E$31,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="D61" s="29">
-        <f>IF('balance_raw_38841297'!$D$31="","—",IF(ABS(D21-'balance_raw_38841297'!$D$31)&lt;=1,"✓ OK","❌ "&amp;TEXT(D21-'balance_raw_38841297'!$D$31,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_38841297'!$D$31="","—",IF(ABS(D21-'balance_raw_38841297'!$D$31)&lt;=1,"✓ OK","❌ "&amp;TEXT(D21-'balance_raw_38841297'!$D$31,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="F61" s="25" t="inlineStr">
@@ -7304,15 +7304,15 @@
         </is>
       </c>
       <c r="B62" s="29">
-        <f>IF('balance_raw_38841297'!$F$58="","—",IF(ABS(B25-'balance_raw_38841297'!$F$58)&lt;=1,"✓ OK","❌ "&amp;TEXT(B25-'balance_raw_38841297'!$F$58,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_38841297'!$F$58="","—",IF(ABS(B25-'balance_raw_38841297'!$F$58)&lt;=1,"✓ OK","❌ "&amp;TEXT(B25-'balance_raw_38841297'!$F$58,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="C62" s="29">
-        <f>IF('balance_raw_38841297'!$E$58="","—",IF(ABS(C25-'balance_raw_38841297'!$E$58)&lt;=1,"✓ OK","❌ "&amp;TEXT(C25-'balance_raw_38841297'!$E$58,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_38841297'!$E$58="","—",IF(ABS(C25-'balance_raw_38841297'!$E$58)&lt;=1,"✓ OK","❌ "&amp;TEXT(C25-'balance_raw_38841297'!$E$58,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="D62" s="29">
-        <f>IF('balance_raw_38841297'!$D$58="","—",IF(ABS(D25-'balance_raw_38841297'!$D$58)&lt;=1,"✓ OK","❌ "&amp;TEXT(D25-'balance_raw_38841297'!$D$58,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_38841297'!$D$58="","—",IF(ABS(D25-'balance_raw_38841297'!$D$58)&lt;=1,"✓ OK","❌ "&amp;TEXT(D25-'balance_raw_38841297'!$D$58,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="F62" s="25" t="inlineStr">
@@ -7328,15 +7328,15 @@
         </is>
       </c>
       <c r="B63" s="29">
-        <f>IF(ABS(B21-B25)&lt;=1,"✓ OK","❌ "&amp;TEXT(B21-B25,"+#,##0;-#,##0")&amp;" t.kr.")</f>
+        <f>IF(ABS(B21-B25)&lt;=1,"✓ OK","❌ "&amp;TEXT(B21-B25,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter")</f>
         <v/>
       </c>
       <c r="C63" s="29">
-        <f>IF(ABS(C21-C25)&lt;=1,"✓ OK","❌ "&amp;TEXT(C21-C25,"+#,##0;-#,##0")&amp;" t.kr.")</f>
+        <f>IF(ABS(C21-C25)&lt;=1,"✓ OK","❌ "&amp;TEXT(C21-C25,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter")</f>
         <v/>
       </c>
       <c r="D63" s="29">
-        <f>IF(ABS(D21-D25)&lt;=1,"✓ OK","❌ "&amp;TEXT(D21-D25,"+#,##0;-#,##0")&amp;" t.kr.")</f>
+        <f>IF(ABS(D21-D25)&lt;=1,"✓ OK","❌ "&amp;TEXT(D21-D25,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter")</f>
         <v/>
       </c>
       <c r="F63" s="25" t="inlineStr">
@@ -7352,15 +7352,15 @@
         </is>
       </c>
       <c r="B64" s="29">
-        <f>IF('res_raw_38841297'!$F$6="","—",IF(ABS(B9-'res_raw_38841297'!$F$6)&lt;=1,"✓ OK","❌ "&amp;TEXT(B9-'res_raw_38841297'!$F$6,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_38841297'!$F$6="","—",IF(ABS(B9-'res_raw_38841297'!$F$6)&lt;=1,"✓ OK","❌ "&amp;TEXT(B9-'res_raw_38841297'!$F$6,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="C64" s="29">
-        <f>IF('res_raw_38841297'!$E$6="","—",IF(ABS(C9-'res_raw_38841297'!$E$6)&lt;=1,"✓ OK","❌ "&amp;TEXT(C9-'res_raw_38841297'!$E$6,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_38841297'!$E$6="","—",IF(ABS(C9-'res_raw_38841297'!$E$6)&lt;=1,"✓ OK","❌ "&amp;TEXT(C9-'res_raw_38841297'!$E$6,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="D64" s="29">
-        <f>IF('res_raw_38841297'!$D$6="","—",IF(ABS(D9-'res_raw_38841297'!$D$6)&lt;=1,"✓ OK","❌ "&amp;TEXT(D9-'res_raw_38841297'!$D$6,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_38841297'!$D$6="","—",IF(ABS(D9-'res_raw_38841297'!$D$6)&lt;=1,"✓ OK","❌ "&amp;TEXT(D9-'res_raw_38841297'!$D$6,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="F64" s="25" t="inlineStr">
@@ -7376,15 +7376,15 @@
         </is>
       </c>
       <c r="B65" s="29">
-        <f>IF('res_raw_38841297'!$F$11="","—",IF(ABS(B13-'res_raw_38841297'!$F$11)&lt;=1,"✓ OK","❌ "&amp;TEXT(B13-'res_raw_38841297'!$F$11,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_38841297'!$F$11="","—",IF(ABS(B13-'res_raw_38841297'!$F$11)&lt;=1,"✓ OK","❌ "&amp;TEXT(B13-'res_raw_38841297'!$F$11,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="C65" s="29">
-        <f>IF('res_raw_38841297'!$E$11="","—",IF(ABS(C13-'res_raw_38841297'!$E$11)&lt;=1,"✓ OK","❌ "&amp;TEXT(C13-'res_raw_38841297'!$E$11,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_38841297'!$E$11="","—",IF(ABS(C13-'res_raw_38841297'!$E$11)&lt;=1,"✓ OK","❌ "&amp;TEXT(C13-'res_raw_38841297'!$E$11,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="D65" s="29">
-        <f>IF('res_raw_38841297'!$D$11="","—",IF(ABS(D13-'res_raw_38841297'!$D$11)&lt;=1,"✓ OK","❌ "&amp;TEXT(D13-'res_raw_38841297'!$D$11,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_38841297'!$D$11="","—",IF(ABS(D13-'res_raw_38841297'!$D$11)&lt;=1,"✓ OK","❌ "&amp;TEXT(D13-'res_raw_38841297'!$D$11,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="F65" s="25" t="inlineStr">
@@ -7400,15 +7400,15 @@
         </is>
       </c>
       <c r="B66" s="29">
-        <f>IF('res_raw_38841297'!$F$16="","—",IF(ABS(B16-'res_raw_38841297'!$F$16)&lt;=1,"✓ OK","❌ "&amp;TEXT(B16-'res_raw_38841297'!$F$16,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_38841297'!$F$16="","—",IF(ABS(B16-'res_raw_38841297'!$F$16)&lt;=1,"✓ OK","❌ "&amp;TEXT(B16-'res_raw_38841297'!$F$16,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="C66" s="29">
-        <f>IF('res_raw_38841297'!$E$16="","—",IF(ABS(C16-'res_raw_38841297'!$E$16)&lt;=1,"✓ OK","❌ "&amp;TEXT(C16-'res_raw_38841297'!$E$16,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_38841297'!$E$16="","—",IF(ABS(C16-'res_raw_38841297'!$E$16)&lt;=1,"✓ OK","❌ "&amp;TEXT(C16-'res_raw_38841297'!$E$16,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="D66" s="29">
-        <f>IF('res_raw_38841297'!$D$16="","—",IF(ABS(D16-'res_raw_38841297'!$D$16)&lt;=1,"✓ OK","❌ "&amp;TEXT(D16-'res_raw_38841297'!$D$16,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_38841297'!$D$16="","—",IF(ABS(D16-'res_raw_38841297'!$D$16)&lt;=1,"✓ OK","❌ "&amp;TEXT(D16-'res_raw_38841297'!$D$16,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="F66" s="25" t="inlineStr">

--- a/filer/38841297_silvan.xlsx
+++ b/filer/38841297_silvan.xlsx
@@ -615,7 +615,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (valuta pr. år - se kolonneoverskrifter)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (valuta pr. år - se kolonneoverskrifter) · Klasse C-stor · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/38841297_silvan.xlsx
+++ b/filer/38841297_silvan.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik_38841297" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw_38841297" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw_38841297" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw_38841297" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -192,9 +193,9 @@
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -595,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L98"/>
+  <dimension ref="A1:L105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -629,7 +630,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -644,35 +645,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1498,35 +1499,35 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -2976,35 +2977,35 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
@@ -4310,19 +4311,19 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
@@ -4428,19 +4429,19 @@
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C87" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
@@ -4737,6 +4738,148 @@
       </c>
       <c r="F98" s="13">
         <f>IFERROR($F$36/($F$61+$F$67)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE valuta pr. år - se kolonneoverskrifter</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B101" s="17">
+        <f>'pengestrom_raw_38841297'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C101" s="17">
+        <f>'pengestrom_raw_38841297'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D101" s="17">
+        <f>'pengestrom_raw_38841297'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E101" s="17">
+        <f>'pengestrom_raw_38841297'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F101" s="17">
+        <f>'pengestrom_raw_38841297'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B102" s="17">
+        <f>'pengestrom_raw_38841297'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C102" s="17">
+        <f>'pengestrom_raw_38841297'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D102" s="17">
+        <f>'pengestrom_raw_38841297'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E102" s="17">
+        <f>'pengestrom_raw_38841297'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F102" s="17">
+        <f>'pengestrom_raw_38841297'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B103" s="17">
+        <f>'pengestrom_raw_38841297'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C103" s="17">
+        <f>'pengestrom_raw_38841297'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D103" s="17">
+        <f>'pengestrom_raw_38841297'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E103" s="17">
+        <f>'pengestrom_raw_38841297'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F103" s="17">
+        <f>'pengestrom_raw_38841297'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B104" s="17">
+        <f>'pengestrom_raw_38841297'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C104" s="17">
+        <f>'pengestrom_raw_38841297'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D104" s="17">
+        <f>'pengestrom_raw_38841297'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E104" s="17">
+        <f>'pengestrom_raw_38841297'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F104" s="17">
+        <f>'pengestrom_raw_38841297'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B105">
+        <f>IF(ABS(('pengestrom_raw_38841297'!$B$2+'pengestrom_raw_38841297'!$B$3+'pengestrom_raw_38841297'!$B$4)-'pengestrom_raw_38841297'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_38841297'!$B$2+'pengestrom_raw_38841297'!$B$3+'pengestrom_raw_38841297'!$B$4)-'pengestrom_raw_38841297'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C105">
+        <f>IF(ABS(('pengestrom_raw_38841297'!$C$2+'pengestrom_raw_38841297'!$C$3+'pengestrom_raw_38841297'!$C$4)-'pengestrom_raw_38841297'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_38841297'!$C$2+'pengestrom_raw_38841297'!$C$3+'pengestrom_raw_38841297'!$C$4)-'pengestrom_raw_38841297'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D105">
+        <f>IF(ABS(('pengestrom_raw_38841297'!$D$2+'pengestrom_raw_38841297'!$D$3+'pengestrom_raw_38841297'!$D$4)-'pengestrom_raw_38841297'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_38841297'!$D$2+'pengestrom_raw_38841297'!$D$3+'pengestrom_raw_38841297'!$D$4)-'pengestrom_raw_38841297'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E105">
+        <f>IF(ABS(('pengestrom_raw_38841297'!$E$2+'pengestrom_raw_38841297'!$E$3+'pengestrom_raw_38841297'!$E$4)-'pengestrom_raw_38841297'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_38841297'!$E$2+'pengestrom_raw_38841297'!$E$3+'pengestrom_raw_38841297'!$E$4)-'pengestrom_raw_38841297'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F105">
+        <f>IF(ABS(('pengestrom_raw_38841297'!$F$2+'pengestrom_raw_38841297'!$F$3+'pengestrom_raw_38841297'!$F$4)-'pengestrom_raw_38841297'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_38841297'!$F$2+'pengestrom_raw_38841297'!$F$3+'pengestrom_raw_38841297'!$F$4)-'pengestrom_raw_38841297'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4769,399 +4912,395 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>1392781</v>
-      </c>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>1241751</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>1327494</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>1365446</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>1394619</v>
       </c>
+      <c r="F2" s="17" t="n">
+        <v>1527139</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
-        <v>3327</v>
-      </c>
-      <c r="C3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>11965</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>13830</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>15709</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>17433</v>
       </c>
+      <c r="F3" s="17" t="n">
+        <v>19440</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Vareforbrug</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>847716</v>
-      </c>
-      <c r="C4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>733061</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>783500</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>832963</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>864923</v>
       </c>
+      <c r="F4" s="17" t="n">
+        <v>967616</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Andre eksterne omkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>214859</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>184335</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>215883</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>232917</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>238503</v>
       </c>
+      <c r="F5" s="17" t="n">
+        <v>235837</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>548392</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>520655</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>557824</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>548192</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>308626</v>
       </c>
+      <c r="F6" s="17" t="n">
+        <v>343126</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Personaleomkostninger</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>250151</v>
-      </c>
-      <c r="C7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>239224</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>249467</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>273658</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>262539</v>
       </c>
+      <c r="F7" s="17" t="n">
+        <v>267701</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Resultat før afskrivninger</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Af- og nedskrivninger</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>24833</v>
-      </c>
-      <c r="C9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>24546</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>25260</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>32334</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>31278</v>
       </c>
+      <c r="F9" s="17" t="n">
+        <v>37059</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
-        <v>103</v>
-      </c>
-      <c r="C10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>-25</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>450</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>0</v>
       </c>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>58446</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>72544</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>67239</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>8833</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>14809</v>
       </c>
+      <c r="F11" s="17" t="n">
+        <v>38366</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>392</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>4617</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>6536</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>7150</v>
       </c>
+      <c r="F13" s="17" t="n">
+        <v>10327</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
-        <v>18635</v>
-      </c>
-      <c r="C14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>6347</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>8082</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>13138</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>16722</v>
       </c>
+      <c r="F14" s="17" t="n">
+        <v>11845</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="16" t="n">
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n">
         <v>-23161</v>
       </c>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
-        <v>39826</v>
-      </c>
-      <c r="C16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>66589</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>63774</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>2231</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>5237</v>
       </c>
+      <c r="F16" s="17" t="n">
+        <v>36848</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
-        <v>8869</v>
-      </c>
-      <c r="C17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>15116</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>14234</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>-1844</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>2179</v>
       </c>
+      <c r="F17" s="17" t="n">
+        <v>8782</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>30957</v>
-      </c>
-      <c r="C18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>51473</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>49540</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>4075</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>3058</v>
       </c>
+      <c r="F18" s="17" t="n">
+        <v>28066</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="17" t="n">
+        <v>597</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>624</v>
+      </c>
+      <c r="D19" s="17" t="n">
         <v>639</v>
       </c>
-      <c r="C19" s="16" t="n">
-        <v>597</v>
-      </c>
-      <c r="D19" s="16" t="n">
-        <v>624</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>639</v>
-      </c>
-      <c r="F19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>599</v>
       </c>
+      <c r="F19" s="17" t="n">
+        <v>565</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
-        <v>15378</v>
-      </c>
-      <c r="C20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>36344</v>
       </c>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5192,1009 +5331,1009 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Udviklingsprojekter</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="16" t="n"/>
-      <c r="D2" s="16" t="n"/>
-      <c r="E2" s="16" t="n"/>
-      <c r="F2" s="16" t="n"/>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="17" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Patenter, varemærker mv.</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n"/>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>8655</v>
-      </c>
-      <c r="C4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>7356</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>6058</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>4760</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>3462</v>
       </c>
+      <c r="F4" s="17" t="n">
+        <v>2164</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>8655</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>7356</v>
       </c>
-      <c r="D5" s="16" t="n"/>
-      <c r="E5" s="16" t="n"/>
-      <c r="F5" s="16" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n">
+        <v>2164</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Grunde og bygninger</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n"/>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Produktionsanlæg og maskiner</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>1986</v>
-      </c>
-      <c r="C7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>1789</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>3285</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>3001</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>3024</v>
       </c>
+      <c r="F7" s="17" t="n">
+        <v>3735</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Driftsmateriel og inventar</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
-        <v>38222</v>
-      </c>
-      <c r="C8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>47666</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>82198</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>98543</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>139900</v>
       </c>
+      <c r="F8" s="17" t="n">
+        <v>127254</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Indretning af lejede lokaler</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>12823</v>
-      </c>
-      <c r="C9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>15586</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>16266</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>30717</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>13660</v>
       </c>
+      <c r="F9" s="17" t="n">
+        <v>12043</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Forudbetaling og anlægsaktiver under opførelse</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
-        <v>14</v>
-      </c>
-      <c r="C10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>971</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>186</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>8967</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>4046</v>
       </c>
+      <c r="F10" s="17" t="n">
+        <v>13363</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>53045</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>66012</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>101935</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>141228</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>160630</v>
       </c>
+      <c r="F11" s="17" t="n">
+        <v>156395</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Deposita</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
-        <v>17823</v>
-      </c>
-      <c r="C13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>17522</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>17582</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>15976</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>17083</v>
       </c>
+      <c r="F13" s="17" t="n">
+        <v>14991</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Finansielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n"/>
+      <c r="F14" s="17" t="n">
+        <v>14991</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
-        <v>79523</v>
-      </c>
-      <c r="C15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>90890</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>125575</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>161964</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>181175</v>
       </c>
+      <c r="F15" s="17" t="n">
+        <v>173550</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Råvarer og hjælpematerialer</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n"/>
-      <c r="D16" s="16" t="n"/>
-      <c r="E16" s="16" t="n"/>
-      <c r="F16" s="16" t="n"/>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="17" t="n"/>
+      <c r="F16" s="17" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Varer under fremstilling</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Færdigvarer og handelsvarer</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>272393</v>
-      </c>
-      <c r="C18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>284091</v>
       </c>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n">
+        <v>333976</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
-        <v>272393</v>
-      </c>
-      <c r="C19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>284091</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>356595</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>315841</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>342973</v>
       </c>
+      <c r="F19" s="17" t="n">
+        <v>333976</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
-        <v>2112</v>
-      </c>
-      <c r="C20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>5479</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="C20" s="17" t="n">
         <v>5610</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <v>14966</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <v>16499</v>
       </c>
+      <c r="F20" s="17" t="n">
+        <v>7310</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
+      <c r="B21" s="17" t="n">
+        <v>40367</v>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>129480</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>136125</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>117811</v>
+      </c>
+      <c r="F21" s="17" t="n">
+        <v>127951</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>Andre tilgodehavender</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>5838</v>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>4648</v>
+      </c>
+      <c r="D22" s="17" t="n">
+        <v>855</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>3149</v>
+      </c>
+      <c r="F22" s="17" t="n">
+        <v>3306</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>Periodeafgrænsningsposter (aktiver)</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n">
+        <v>13187</v>
+      </c>
+      <c r="C23" s="17" t="n"/>
+      <c r="D23" s="17" t="n"/>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="17" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>Udskudt skatteaktiv</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n">
+        <v>15246</v>
+      </c>
+      <c r="C24" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="16" t="n">
-        <v>40367</v>
-      </c>
-      <c r="D21" s="16" t="n">
-        <v>129480</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>136125</v>
-      </c>
-      <c r="F21" s="16" t="n">
-        <v>117811</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>Andre tilgodehavender</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="n">
-        <v>4436</v>
-      </c>
-      <c r="C22" s="16" t="n">
-        <v>5838</v>
-      </c>
-      <c r="D22" s="16" t="n">
-        <v>4648</v>
-      </c>
-      <c r="E22" s="16" t="n">
-        <v>855</v>
-      </c>
-      <c r="F22" s="16" t="n">
-        <v>3149</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>Periodeafgrænsningsposter (aktiver)</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="n">
-        <v>12824</v>
-      </c>
-      <c r="C23" s="16" t="n">
-        <v>13187</v>
-      </c>
-      <c r="D23" s="16" t="n"/>
-      <c r="E23" s="16" t="n"/>
-      <c r="F23" s="16" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>Udskudt skatteaktiv</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="n">
-        <v>28365</v>
-      </c>
-      <c r="C24" s="16" t="n">
-        <v>15246</v>
-      </c>
-      <c r="D24" s="16" t="n">
+      <c r="D24" s="17" t="n">
+        <v>1858</v>
+      </c>
+      <c r="E24" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="16" t="n">
-        <v>1858</v>
-      </c>
-      <c r="F24" s="16" t="n">
+      <c r="F24" s="17" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>Kortfristede skattetilgodehavender</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="17" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Tilgodehavender</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="n">
+        <v>80117</v>
+      </c>
+      <c r="C27" s="17" t="n">
+        <v>154691</v>
+      </c>
+      <c r="D27" s="17" t="n">
+        <v>173180</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>145537</v>
+      </c>
+      <c r="F27" s="17" t="n">
+        <v>154657</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>Værdipapirer</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>Likvide beholdninger</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="n">
+        <v>51064</v>
+      </c>
+      <c r="C29" s="17" t="n">
+        <v>27903</v>
+      </c>
+      <c r="D29" s="17" t="n">
+        <v>28345</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>26146</v>
+      </c>
+      <c r="F29" s="17" t="n">
+        <v>18027</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>Omsætningsaktiver</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="n">
+        <v>415272</v>
+      </c>
+      <c r="C30" s="17" t="n">
+        <v>539189</v>
+      </c>
+      <c r="D30" s="17" t="n">
+        <v>517366</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>514656</v>
+      </c>
+      <c r="F30" s="17" t="n">
+        <v>506660</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>Aktiver</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="n">
+        <v>506162</v>
+      </c>
+      <c r="C31" s="17" t="n">
+        <v>664764</v>
+      </c>
+      <c r="D31" s="17" t="n">
+        <v>679330</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>695831</v>
+      </c>
+      <c r="F31" s="17" t="n">
+        <v>680210</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>Selskabskapital</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C32" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D32" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F32" s="17" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="17" t="n"/>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="17" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>Reserve for udviklingsomkostninger</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>Reserve for sikringstransaktioner</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="17" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>Andre reserver</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="17" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>Overført resultat</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="n">
+        <v>73577</v>
+      </c>
+      <c r="C37" s="17" t="n">
+        <v>98617</v>
+      </c>
+      <c r="D37" s="17" t="n">
+        <v>77692</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>80750</v>
+      </c>
+      <c r="F37" s="17" t="n">
+        <v>38816</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>Egenkapital i alt</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="n">
+        <v>74577</v>
+      </c>
+      <c r="C38" s="17" t="n">
+        <v>124117</v>
+      </c>
+      <c r="D38" s="17" t="n">
+        <v>103692</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>81750</v>
+      </c>
+      <c r="F38" s="17" t="n">
+        <v>109816</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>Hensatte forpligtelser</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="n">
+        <v>1120</v>
+      </c>
+      <c r="C39" s="17" t="n">
+        <v>1070</v>
+      </c>
+      <c r="D39" s="17" t="n">
+        <v>1656</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>4850</v>
+      </c>
+      <c r="F39" s="17" t="n">
+        <v>4821</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (langfristet)</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="17" t="n"/>
+      <c r="D40" s="17" t="n"/>
+      <c r="E40" s="17" t="n"/>
+      <c r="F40" s="17" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>Langfristede lån</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C41" s="17" t="n">
+        <v>115096</v>
+      </c>
+      <c r="D41" s="17" t="n">
+        <v>105000</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>105000</v>
+      </c>
+      <c r="F41" s="17" t="n">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>Leasingforpligtelser (langfristet)</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="n"/>
+      <c r="C42" s="17" t="n"/>
+      <c r="D42" s="17" t="n"/>
+      <c r="E42" s="17" t="n"/>
+      <c r="F42" s="17" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>Anden gæld (langfristet)</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="17" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>Langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="n"/>
+      <c r="C44" s="17" t="n"/>
+      <c r="D44" s="17" t="n">
+        <v>124379</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>125022</v>
+      </c>
+      <c r="F44" s="17" t="n">
+        <v>65815</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="n"/>
+      <c r="C45" s="17" t="n"/>
+      <c r="D45" s="17" t="n"/>
+      <c r="E45" s="17" t="n"/>
+      <c r="F45" s="17" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="17" t="n"/>
+      <c r="F46" s="17" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>Kreditinstitutter</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="n"/>
+      <c r="C47" s="17" t="n"/>
+      <c r="D47" s="17" t="n"/>
+      <c r="E47" s="17" t="n"/>
+      <c r="F47" s="17" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>Leasingforpligtelser (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="n"/>
+      <c r="C48" s="17" t="n"/>
+      <c r="D48" s="17" t="n"/>
+      <c r="E48" s="17" t="n"/>
+      <c r="F48" s="17" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>Leverandører af varer og tjenesteydelser</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="n">
+        <v>291617</v>
+      </c>
+      <c r="C49" s="17" t="n">
+        <v>318330</v>
+      </c>
+      <c r="D49" s="17" t="n">
+        <v>339898</v>
+      </c>
+      <c r="E49" s="17" t="n">
+        <v>404135</v>
+      </c>
+      <c r="F49" s="17" t="n">
+        <v>411206</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>Gæld til tilknyttede virksomheder</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="C50" s="17" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>Kortfristede skattetilgodehavender</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="16" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="16" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>Tilgodehavender</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n">
-        <v>47737</v>
-      </c>
-      <c r="C27" s="16" t="n">
-        <v>80117</v>
-      </c>
-      <c r="D27" s="16" t="n">
-        <v>154691</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>173180</v>
-      </c>
-      <c r="F27" s="16" t="n">
-        <v>145537</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>Værdipapirer</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>Likvide beholdninger</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="n">
-        <v>156577</v>
-      </c>
-      <c r="C29" s="16" t="n">
-        <v>51064</v>
-      </c>
-      <c r="D29" s="16" t="n">
-        <v>27903</v>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>28345</v>
-      </c>
-      <c r="F29" s="16" t="n">
-        <v>26146</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
-          <t>Omsætningsaktiver</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="n">
-        <v>476707</v>
-      </c>
-      <c r="C30" s="16" t="n">
-        <v>415272</v>
-      </c>
-      <c r="D30" s="16" t="n">
-        <v>539189</v>
-      </c>
-      <c r="E30" s="16" t="n">
-        <v>517366</v>
-      </c>
-      <c r="F30" s="16" t="n">
-        <v>514656</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>Aktiver</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="n">
-        <v>556230</v>
-      </c>
-      <c r="C31" s="16" t="n">
+      <c r="D50" s="17" t="n"/>
+      <c r="E50" s="17" t="n"/>
+      <c r="F50" s="17" t="n">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="n"/>
+      <c r="C51" s="17" t="n"/>
+      <c r="D51" s="17" t="n"/>
+      <c r="E51" s="17" t="n"/>
+      <c r="F51" s="17" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>Selskabsskat</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="n"/>
+      <c r="C52" s="17" t="n">
+        <v>762</v>
+      </c>
+      <c r="D52" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="17" t="n"/>
+      <c r="F52" s="17" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="n"/>
+      <c r="C53" s="17" t="n"/>
+      <c r="D53" s="17" t="n"/>
+      <c r="E53" s="17" t="n"/>
+      <c r="F53" s="17" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>Anden gæld (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="n">
+        <v>121062</v>
+      </c>
+      <c r="C54" s="17" t="n">
+        <v>97446</v>
+      </c>
+      <c r="D54" s="17" t="n">
+        <v>104504</v>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>74748</v>
+      </c>
+      <c r="F54" s="17" t="n">
+        <v>83197</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>Periodeafgrænsningsposter (passiver)</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="n">
+        <v>7721</v>
+      </c>
+      <c r="C55" s="17" t="n">
+        <v>7943</v>
+      </c>
+      <c r="D55" s="17" t="n">
+        <v>5201</v>
+      </c>
+      <c r="E55" s="17" t="n">
+        <v>5326</v>
+      </c>
+      <c r="F55" s="17" t="n">
+        <v>4780</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="inlineStr">
+        <is>
+          <t>Kortfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="n">
+        <v>420465</v>
+      </c>
+      <c r="C56" s="17" t="n">
+        <v>424481</v>
+      </c>
+      <c r="D56" s="17" t="n">
+        <v>449603</v>
+      </c>
+      <c r="E56" s="17" t="n">
+        <v>484209</v>
+      </c>
+      <c r="F56" s="17" t="n">
+        <v>499758</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="15" t="inlineStr">
+        <is>
+          <t>Gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="n">
+        <v>430465</v>
+      </c>
+      <c r="C57" s="17" t="n">
+        <v>539577</v>
+      </c>
+      <c r="D57" s="17" t="n">
+        <v>573982</v>
+      </c>
+      <c r="E57" s="17" t="n">
+        <v>609231</v>
+      </c>
+      <c r="F57" s="17" t="n">
+        <v>565573</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="inlineStr">
+        <is>
+          <t>Passiver</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="n">
         <v>506162</v>
       </c>
-      <c r="D31" s="16" t="n">
+      <c r="C58" s="17" t="n">
         <v>664764</v>
       </c>
-      <c r="E31" s="16" t="n">
+      <c r="D58" s="17" t="n">
         <v>679330</v>
       </c>
-      <c r="F31" s="16" t="n">
+      <c r="E58" s="17" t="n">
         <v>695831</v>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t>Selskabskapital</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C32" s="16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D32" s="16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E32" s="16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F32" s="16" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="n"/>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="16" t="n"/>
-      <c r="E33" s="16" t="n"/>
-      <c r="F33" s="16" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="inlineStr">
-        <is>
-          <t>Reserve for udviklingsomkostninger</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="16" t="n"/>
-      <c r="D34" s="16" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="16" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="15" t="inlineStr">
-        <is>
-          <t>Reserve for sikringstransaktioner</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="inlineStr">
-        <is>
-          <t>Andre reserver</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="n"/>
-      <c r="C36" s="16" t="n"/>
-      <c r="D36" s="16" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="16" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="15" t="inlineStr">
-        <is>
-          <t>Overført resultat</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="n">
-        <v>22104</v>
-      </c>
-      <c r="C37" s="16" t="n">
-        <v>73577</v>
-      </c>
-      <c r="D37" s="16" t="n">
-        <v>98617</v>
-      </c>
-      <c r="E37" s="16" t="n">
-        <v>77692</v>
-      </c>
-      <c r="F37" s="16" t="n">
-        <v>80750</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t>Egenkapital i alt</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="n">
-        <v>23104</v>
-      </c>
-      <c r="C38" s="16" t="n">
-        <v>74577</v>
-      </c>
-      <c r="D38" s="16" t="n">
-        <v>124117</v>
-      </c>
-      <c r="E38" s="16" t="n">
-        <v>103692</v>
-      </c>
-      <c r="F38" s="16" t="n">
-        <v>81750</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="17" t="inlineStr">
-        <is>
-          <t>Hensatte forpligtelser</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="n">
-        <v>1195</v>
-      </c>
-      <c r="C39" s="16" t="n">
-        <v>1120</v>
-      </c>
-      <c r="D39" s="16" t="n">
-        <v>1070</v>
-      </c>
-      <c r="E39" s="16" t="n">
-        <v>1656</v>
-      </c>
-      <c r="F39" s="16" t="n">
-        <v>4850</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="inlineStr">
-        <is>
-          <t>Ansvarlig lånekapital (langfristet)</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="n"/>
-      <c r="C40" s="16" t="n"/>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="16" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="15" t="inlineStr">
-        <is>
-          <t>Langfristede lån</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="n">
-        <v>140000</v>
-      </c>
-      <c r="C41" s="16" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D41" s="16" t="n">
-        <v>115096</v>
-      </c>
-      <c r="E41" s="16" t="n">
-        <v>105000</v>
-      </c>
-      <c r="F41" s="16" t="n">
-        <v>105000</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>Leasingforpligtelser (langfristet)</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="15" t="inlineStr">
-        <is>
-          <t>Anden gæld (langfristet)</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="16" t="n"/>
-      <c r="D43" s="16" t="n"/>
-      <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="17" t="inlineStr">
-        <is>
-          <t>Langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="n"/>
-      <c r="C44" s="16" t="n"/>
-      <c r="D44" s="16" t="n"/>
-      <c r="E44" s="16" t="n">
-        <v>124379</v>
-      </c>
-      <c r="F44" s="16" t="n">
-        <v>125022</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="15" t="inlineStr">
-        <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="16" t="n"/>
-      <c r="D45" s="16" t="n"/>
-      <c r="E45" s="16" t="n"/>
-      <c r="F45" s="16" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="16" t="n"/>
-      <c r="D46" s="16" t="n"/>
-      <c r="E46" s="16" t="n"/>
-      <c r="F46" s="16" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="15" t="inlineStr">
-        <is>
-          <t>Kreditinstitutter</t>
-        </is>
-      </c>
-      <c r="B47" s="16" t="n"/>
-      <c r="C47" s="16" t="n"/>
-      <c r="D47" s="16" t="n"/>
-      <c r="E47" s="16" t="n"/>
-      <c r="F47" s="16" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="15" t="inlineStr">
-        <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="n"/>
-      <c r="C48" s="16" t="n"/>
-      <c r="D48" s="16" t="n"/>
-      <c r="E48" s="16" t="n"/>
-      <c r="F48" s="16" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="15" t="inlineStr">
-        <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
-        </is>
-      </c>
-      <c r="B49" s="16" t="n">
-        <v>261255</v>
-      </c>
-      <c r="C49" s="16" t="n">
-        <v>291617</v>
-      </c>
-      <c r="D49" s="16" t="n">
-        <v>318330</v>
-      </c>
-      <c r="E49" s="16" t="n">
-        <v>339898</v>
-      </c>
-      <c r="F49" s="16" t="n">
-        <v>404135</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="15" t="inlineStr">
-        <is>
-          <t>Gæld til tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B50" s="16" t="n">
-        <v>521</v>
-      </c>
-      <c r="C50" s="16" t="n">
-        <v>65</v>
-      </c>
-      <c r="D50" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="16" t="n"/>
-      <c r="F50" s="16" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="15" t="inlineStr">
-        <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
-        </is>
-      </c>
-      <c r="B51" s="16" t="n"/>
-      <c r="C51" s="16" t="n"/>
-      <c r="D51" s="16" t="n"/>
-      <c r="E51" s="16" t="n"/>
-      <c r="F51" s="16" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="15" t="inlineStr">
-        <is>
-          <t>Selskabsskat</t>
-        </is>
-      </c>
-      <c r="B52" s="16" t="n"/>
-      <c r="C52" s="16" t="n"/>
-      <c r="D52" s="16" t="n">
-        <v>762</v>
-      </c>
-      <c r="E52" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="16" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="15" t="inlineStr">
-        <is>
-          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
-        </is>
-      </c>
-      <c r="B53" s="16" t="n"/>
-      <c r="C53" s="16" t="n"/>
-      <c r="D53" s="16" t="n"/>
-      <c r="E53" s="16" t="n"/>
-      <c r="F53" s="16" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="15" t="inlineStr">
-        <is>
-          <t>Anden gæld (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B54" s="16" t="n">
-        <v>122063</v>
-      </c>
-      <c r="C54" s="16" t="n">
-        <v>121062</v>
-      </c>
-      <c r="D54" s="16" t="n">
-        <v>97446</v>
-      </c>
-      <c r="E54" s="16" t="n">
-        <v>104504</v>
-      </c>
-      <c r="F54" s="16" t="n">
-        <v>74748</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="15" t="inlineStr">
-        <is>
-          <t>Periodeafgrænsningsposter (passiver)</t>
-        </is>
-      </c>
-      <c r="B55" s="16" t="n">
-        <v>8092</v>
-      </c>
-      <c r="C55" s="16" t="n">
-        <v>7721</v>
-      </c>
-      <c r="D55" s="16" t="n">
-        <v>7943</v>
-      </c>
-      <c r="E55" s="16" t="n">
-        <v>5201</v>
-      </c>
-      <c r="F55" s="16" t="n">
-        <v>5326</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="17" t="inlineStr">
-        <is>
-          <t>Kortfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B56" s="16" t="n">
-        <v>391931</v>
-      </c>
-      <c r="C56" s="16" t="n">
-        <v>420465</v>
-      </c>
-      <c r="D56" s="16" t="n">
-        <v>424481</v>
-      </c>
-      <c r="E56" s="16" t="n">
-        <v>449603</v>
-      </c>
-      <c r="F56" s="16" t="n">
-        <v>484209</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="17" t="inlineStr">
-        <is>
-          <t>Gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B57" s="16" t="n">
-        <v>531931</v>
-      </c>
-      <c r="C57" s="16" t="n">
-        <v>430465</v>
-      </c>
-      <c r="D57" s="16" t="n">
-        <v>539577</v>
-      </c>
-      <c r="E57" s="16" t="n">
-        <v>573982</v>
-      </c>
-      <c r="F57" s="16" t="n">
-        <v>609231</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="17" t="inlineStr">
-        <is>
-          <t>Passiver</t>
-        </is>
-      </c>
-      <c r="B58" s="16" t="n">
-        <v>556230</v>
-      </c>
-      <c r="C58" s="16" t="n">
-        <v>506162</v>
-      </c>
-      <c r="D58" s="16" t="n">
-        <v>664764</v>
-      </c>
-      <c r="E58" s="16" t="n">
-        <v>679330</v>
-      </c>
-      <c r="F58" s="16" t="n">
-        <v>695831</v>
+      <c r="F58" s="17" t="n">
+        <v>680210</v>
       </c>
     </row>
   </sheetData>
@@ -6203,6 +6342,128 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (valuta pr. år - se kolonneoverskrifter)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>100529</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>16649</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>104139</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>48289</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>81172</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>-36042</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>-60264</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>-68727</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>-50488</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>-29291</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>-170000</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>20454</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>-34970</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>-60000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6233,13 +6494,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -6953,7 +7214,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -7071,7 +7332,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -7247,7 +7508,7 @@
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B58" s="29" t="n"/>
